--- a/Data/National Accounts/PSA-09MAQ_2018PSNA_Ann.xlsx
+++ b/Data/National Accounts/PSA-09MAQ_2018PSNA_Ann.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Annl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Annl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4E34E1-20B4-4783-BC11-3ED961BC14EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6624E594-6D78-42D0-8B7F-2122DC9807CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MAQ" sheetId="1" r:id="rId1"/>
@@ -625,9 +625,6 @@
     <t>2023 - 2024</t>
   </si>
   <si>
-    <t>As of January 2026</t>
-  </si>
-  <si>
     <t>Annual 2000 to 2025</t>
   </si>
   <si>
@@ -635,6 +632,9 @@
   </si>
   <si>
     <t>2024 - 2025</t>
+  </si>
+  <si>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -779,15 +779,7 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal 2 2" xfId="3" xr:uid="{9C7F51BC-3441-449C-80EF-173BCCCC4E66}"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -23618,7 +23610,7 @@
     </row>
     <row r="3" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -23629,7 +23621,7 @@
     </row>
     <row r="6" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -23832,10 +23824,10 @@
         <v>37307.881236111294</v>
       </c>
       <c r="Z12" s="8">
-        <v>34369.988174988612</v>
+        <v>34380.176086619416</v>
       </c>
       <c r="AA12" s="8">
-        <v>35167.655241642889</v>
+        <v>35437.721800503627</v>
       </c>
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
@@ -23987,7 +23979,7 @@
         <v>20436.815164513264</v>
       </c>
       <c r="AA13" s="8">
-        <v>21273.033181372237</v>
+        <v>21358.743740910759</v>
       </c>
       <c r="AB13" s="9"/>
       <c r="AC13" s="9"/>
@@ -24136,10 +24128,10 @@
         <v>54126.480717317194</v>
       </c>
       <c r="Z14" s="8">
-        <v>65044.216692288828</v>
+        <v>65055.704060024422</v>
       </c>
       <c r="AA14" s="8">
-        <v>91443.410190239811</v>
+        <v>91538.739621129207</v>
       </c>
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
@@ -24288,10 +24280,10 @@
         <v>43017.59940863432</v>
       </c>
       <c r="Z15" s="8">
-        <v>34712.466067038935</v>
+        <v>34979.858098069337</v>
       </c>
       <c r="AA15" s="8">
-        <v>35126.175353995954</v>
+        <v>35393.338122332134</v>
       </c>
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
@@ -24443,7 +24435,7 @@
         <v>15845.929219488527</v>
       </c>
       <c r="AA16" s="8">
-        <v>15952.361731059738</v>
+        <v>15764.136101405926</v>
       </c>
       <c r="AB16" s="9"/>
       <c r="AC16" s="9"/>
@@ -24592,10 +24584,10 @@
         <v>59191.385112734606</v>
       </c>
       <c r="Z17" s="8">
-        <v>63463.198363521995</v>
+        <v>63468.030767903896</v>
       </c>
       <c r="AA17" s="8">
-        <v>65925.285282273311</v>
+        <v>65590.076582724665</v>
       </c>
       <c r="AB17" s="9"/>
       <c r="AC17" s="9"/>
@@ -24841,10 +24833,10 @@
         <v>232171.30359314874</v>
       </c>
       <c r="Z19" s="12">
-        <v>233872.61368184013</v>
+        <v>234166.51339661886</v>
       </c>
       <c r="AA19" s="12">
-        <v>264887.92098058393</v>
+        <v>265082.75596900634</v>
       </c>
       <c r="AB19" s="9"/>
       <c r="AC19" s="9"/>
@@ -25156,7 +25148,7 @@
     </row>
     <row r="26" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -25167,7 +25159,7 @@
     </row>
     <row r="29" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -25370,10 +25362,10 @@
         <v>24160.990726286</v>
       </c>
       <c r="Z35" s="8">
-        <v>26401.218345692116</v>
+        <v>26411.45190092281</v>
       </c>
       <c r="AA35" s="8">
-        <v>31391.635392424207</v>
+        <v>31645.523754854068</v>
       </c>
       <c r="AB35" s="9"/>
       <c r="AC35" s="9"/>
@@ -25525,7 +25517,7 @@
         <v>17874.80458516434</v>
       </c>
       <c r="AA36" s="8">
-        <v>15329.471144163461</v>
+        <v>15378.519354970096</v>
       </c>
       <c r="AB36" s="9"/>
       <c r="AC36" s="9"/>
@@ -25674,10 +25666,10 @@
         <v>29790.829426211243</v>
       </c>
       <c r="Z37" s="8">
-        <v>28638.231742390646</v>
+        <v>28643.218234691409</v>
       </c>
       <c r="AA37" s="8">
-        <v>28198.215923143445</v>
+        <v>28229.484952219289</v>
       </c>
       <c r="AB37" s="9"/>
       <c r="AC37" s="9"/>
@@ -25826,10 +25818,10 @@
         <v>21992.629915083504</v>
       </c>
       <c r="Z38" s="8">
-        <v>21430.08373956272</v>
+        <v>21594.12717588367</v>
       </c>
       <c r="AA38" s="8">
-        <v>22139.928349778093</v>
+        <v>22303.817579073344</v>
       </c>
       <c r="AB38" s="9"/>
       <c r="AC38" s="9"/>
@@ -25981,7 +25973,7 @@
         <v>8660.5912946055923</v>
       </c>
       <c r="AA39" s="8">
-        <v>8167.9986861035022</v>
+        <v>8125.4955880448369</v>
       </c>
       <c r="AB39" s="9"/>
       <c r="AC39" s="9"/>
@@ -26130,10 +26122,10 @@
         <v>50549.973817958948</v>
       </c>
       <c r="Z40" s="8">
-        <v>54088.562420376264</v>
+        <v>54088.104646659434</v>
       </c>
       <c r="AA40" s="8">
-        <v>55743.61800939517</v>
+        <v>55412.40952531244</v>
       </c>
       <c r="AB40" s="9"/>
       <c r="AC40" s="9"/>
@@ -26379,10 +26371,10 @@
         <v>155251.06421158146</v>
       </c>
       <c r="Z42" s="12">
-        <v>157093.49212779169</v>
+        <v>157272.29783792724</v>
       </c>
       <c r="AA42" s="12">
-        <v>160970.86750500789</v>
+        <v>161095.25075447408</v>
       </c>
       <c r="AB42" s="9"/>
       <c r="AC42" s="9"/>
@@ -26694,7 +26686,7 @@
     </row>
     <row r="49" spans="1:90" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="50" spans="1:90" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -26705,7 +26697,7 @@
     </row>
     <row r="52" spans="1:90" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53" spans="1:90" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -26822,7 +26814,7 @@
         <v>50</v>
       </c>
       <c r="Z56" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AA56" s="17"/>
     </row>
@@ -26903,10 +26895,10 @@
         <v>-48.057264827444037</v>
       </c>
       <c r="Y58" s="18">
-        <v>-7.8747250280163854</v>
+        <v>-7.8474173619328269</v>
       </c>
       <c r="Z58" s="18">
-        <v>2.3208243849055066</v>
+        <v>3.0760334421201492</v>
       </c>
       <c r="AA58" s="18"/>
       <c r="AB58" s="9"/>
@@ -27050,7 +27042,7 @@
         <v>-16.340498115208632</v>
       </c>
       <c r="Z59" s="18">
-        <v>4.0917237354624234</v>
+        <v>4.5111166733960744</v>
       </c>
       <c r="AA59" s="18"/>
       <c r="AB59" s="9"/>
@@ -27191,10 +27183,10 @@
         <v>16.75747134009093</v>
       </c>
       <c r="Y60" s="18">
-        <v>20.170784854812524</v>
+        <v>20.192008048309233</v>
       </c>
       <c r="Z60" s="18">
-        <v>40.586534576686915</v>
+        <v>40.708245254973946</v>
       </c>
       <c r="AA60" s="18"/>
       <c r="AB60" s="9"/>
@@ -27335,10 +27327,10 @@
         <v>6.2675387924184776</v>
       </c>
       <c r="Y61" s="18">
-        <v>-19.306361711872782</v>
+        <v>-18.684774187914542</v>
       </c>
       <c r="Z61" s="18">
-        <v>1.191817620096586</v>
+        <v>1.182051748476411</v>
       </c>
       <c r="AA61" s="18"/>
       <c r="AB61" s="9"/>
@@ -27482,7 +27474,7 @@
         <v>12.387315973160412</v>
       </c>
       <c r="Z62" s="18">
-        <v>0.67167100204076746</v>
+        <v>-0.5161774797151395</v>
       </c>
       <c r="AA62" s="18"/>
       <c r="AB62" s="9"/>
@@ -27623,10 +27615,10 @@
         <v>12.848618166599366</v>
       </c>
       <c r="Y63" s="18">
-        <v>7.216950984761354</v>
+        <v>7.2251150180454147</v>
       </c>
       <c r="Z63" s="18">
-        <v>3.8795506407481923</v>
+        <v>3.3434877199528472</v>
       </c>
       <c r="AA63" s="18"/>
       <c r="AB63" s="9"/>
@@ -27858,10 +27850,10 @@
         <v>-17.15546101922439</v>
       </c>
       <c r="Y65" s="18">
-        <v>0.7327822441281171</v>
+        <v>0.85936968634439381</v>
       </c>
       <c r="Z65" s="18">
-        <v>13.261624270782278</v>
+        <v>13.202674508811256</v>
       </c>
       <c r="AA65" s="18"/>
       <c r="AB65" s="9"/>
@@ -28156,7 +28148,7 @@
     </row>
     <row r="72" spans="1:90" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="73" spans="1:90" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -28167,7 +28159,7 @@
     </row>
     <row r="75" spans="1:90" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="76" spans="1:90" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -28284,7 +28276,7 @@
         <v>50</v>
       </c>
       <c r="Z79" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AA79" s="6"/>
     </row>
@@ -28365,10 +28357,10 @@
         <v>1.5940647708132758</v>
       </c>
       <c r="Y81" s="18">
-        <v>9.2720850928056393</v>
+        <v>9.3144407865212884</v>
       </c>
       <c r="Z81" s="18">
-        <v>18.902222546659004</v>
+        <v>19.817433261775292</v>
       </c>
       <c r="AA81" s="18"/>
       <c r="AB81" s="9"/>
@@ -28512,7 +28504,7 @@
         <v>-10.965494732270713</v>
       </c>
       <c r="Z82" s="18">
-        <v>-14.239783315524718</v>
+        <v>-13.96538473078526</v>
       </c>
       <c r="AA82" s="18"/>
       <c r="AB82" s="9"/>
@@ -28653,10 +28645,10 @@
         <v>7.2248753224308615</v>
       </c>
       <c r="Y83" s="18">
-        <v>-3.86896808857054</v>
+        <v>-3.8522297419155365</v>
       </c>
       <c r="Z83" s="18">
-        <v>-1.536462946474046</v>
+        <v>-1.4444371406947027</v>
       </c>
       <c r="AA83" s="18"/>
       <c r="AB83" s="9"/>
@@ -28797,10 +28789,10 @@
         <v>18.482784219728956</v>
       </c>
       <c r="Y84" s="18">
-        <v>-2.5578849718876313</v>
+        <v>-1.8119831086073219</v>
       </c>
       <c r="Z84" s="18">
-        <v>3.3123744117943232</v>
+        <v>3.2864972842350255</v>
       </c>
       <c r="AA84" s="18"/>
       <c r="AB84" s="9"/>
@@ -28944,7 +28936,7 @@
         <v>-0.22789913748808033</v>
       </c>
       <c r="Z85" s="18">
-        <v>-5.6877480040988644</v>
+        <v>-6.1785123943448212</v>
       </c>
       <c r="AA85" s="18"/>
       <c r="AB85" s="9"/>
@@ -29085,10 +29077,10 @@
         <v>7.5767019762143804</v>
       </c>
       <c r="Y86" s="18">
-        <v>7.0001789024866952</v>
+        <v>6.9992733160298712</v>
       </c>
       <c r="Z86" s="18">
-        <v>3.0598993853003833</v>
+        <v>2.4484216766408764</v>
       </c>
       <c r="AA86" s="18"/>
       <c r="AB86" s="9"/>
@@ -29320,10 +29312,10 @@
         <v>2.0159182219815079</v>
       </c>
       <c r="Y88" s="18">
-        <v>1.1867409254594889</v>
+        <v>1.3019128961275044</v>
       </c>
       <c r="Z88" s="18">
-        <v>2.468196056181668</v>
+        <v>2.4307859483851928</v>
       </c>
       <c r="AA88" s="18"/>
       <c r="AB88" s="9"/>
@@ -29619,7 +29611,7 @@
     </row>
     <row r="94" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="95" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -29630,7 +29622,7 @@
     </row>
     <row r="97" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="98" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -29833,10 +29825,10 @@
         <v>154.41370620420008</v>
       </c>
       <c r="Z103" s="19">
-        <v>130.18334125703998</v>
+        <v>130.17147340324058</v>
       </c>
       <c r="AA103" s="19">
-        <v>112.02874524380452</v>
+        <v>111.98336319229945</v>
       </c>
       <c r="AB103" s="9"/>
       <c r="AC103" s="9"/>
@@ -29988,7 +29980,7 @@
         <v>114.33308301157783</v>
       </c>
       <c r="AA104" s="19">
-        <v>138.77212710936689</v>
+        <v>138.88686711577307</v>
       </c>
       <c r="AB104" s="9"/>
       <c r="AC104" s="9"/>
@@ -30137,10 +30129,10 @@
         <v>181.68839793931485</v>
       </c>
       <c r="Z105" s="19">
-        <v>227.12371796338812</v>
+        <v>227.12428305710358</v>
       </c>
       <c r="AA105" s="19">
-        <v>324.2879281422496</v>
+        <v>324.26641781125659</v>
       </c>
       <c r="AB105" s="9"/>
       <c r="AC105" s="9"/>
@@ -30289,10 +30281,10 @@
         <v>195.60006954480227</v>
       </c>
       <c r="Z106" s="19">
-        <v>161.98007664783506</v>
+        <v>161.98783036313159</v>
       </c>
       <c r="AA106" s="19">
-        <v>158.65532534276707</v>
+        <v>158.68735474029384</v>
       </c>
       <c r="AB106" s="9"/>
       <c r="AC106" s="9"/>
@@ -30444,7 +30436,7 @@
         <v>182.96590475708575</v>
       </c>
       <c r="AA107" s="19">
-        <v>195.30318679164384</v>
+        <v>194.00830300861813</v>
       </c>
       <c r="AB107" s="9"/>
       <c r="AC107" s="9"/>
@@ -30593,10 +30585,10 @@
         <v>117.0947888635812</v>
       </c>
       <c r="Z108" s="19">
-        <v>117.33201165578421</v>
+        <v>117.34193901324619</v>
       </c>
       <c r="AA108" s="19">
-        <v>118.26517121863547</v>
+        <v>118.36712596437997</v>
       </c>
       <c r="AB108" s="9"/>
       <c r="AC108" s="9"/>
@@ -30842,10 +30834,10 @@
         <v>149.54570828367252</v>
       </c>
       <c r="Z110" s="19">
-        <v>148.87479456602219</v>
+        <v>148.89240928999007</v>
       </c>
       <c r="AA110" s="19">
-        <v>164.55643501600881</v>
+        <v>164.5503233195993</v>
       </c>
       <c r="AB110" s="9"/>
       <c r="AC110" s="9"/>
@@ -30963,7 +30955,7 @@
     </row>
     <row r="117" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="118" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -30974,7 +30966,7 @@
     </row>
     <row r="120" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="121" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -31177,10 +31169,10 @@
         <v>16.069118215181625</v>
       </c>
       <c r="Z126" s="19">
-        <v>14.696029446930234</v>
+        <v>14.681935340766719</v>
       </c>
       <c r="AA126" s="19">
-        <v>13.276428427334992</v>
+        <v>13.368550387580486</v>
       </c>
       <c r="AB126" s="9"/>
       <c r="AC126" s="9"/>
@@ -31329,10 +31321,10 @@
         <v>10.521784504108306</v>
       </c>
       <c r="Z127" s="19">
-        <v>8.7384387777508099</v>
+        <v>8.7274712631086011</v>
       </c>
       <c r="AA127" s="19">
-        <v>8.0309563012997991</v>
+        <v>8.0573870838312995</v>
       </c>
       <c r="AB127" s="9"/>
       <c r="AC127" s="9"/>
@@ -31481,10 +31473,10 @@
         <v>23.313165701204444</v>
       </c>
       <c r="Z128" s="19">
-        <v>27.811814161693537</v>
+        <v>27.781813512266169</v>
       </c>
       <c r="AA128" s="19">
-        <v>34.521547774518012</v>
+        <v>34.532136685583566</v>
       </c>
       <c r="AB128" s="9"/>
       <c r="AC128" s="9"/>
@@ -31633,10 +31625,10 @@
         <v>18.528387764931235</v>
       </c>
       <c r="Z129" s="19">
-        <v>14.842467239136306</v>
+        <v>14.938027470572749</v>
       </c>
       <c r="AA129" s="19">
-        <v>13.260769016557262</v>
+        <v>13.351807058498496</v>
       </c>
       <c r="AB129" s="9"/>
       <c r="AC129" s="9"/>
@@ -31785,10 +31777,10 @@
         <v>6.0728404655075554</v>
       </c>
       <c r="Z130" s="19">
-        <v>6.775453085347265</v>
+        <v>6.7669492916134981</v>
       </c>
       <c r="AA130" s="19">
-        <v>6.0223062161558634</v>
+        <v>5.9468734749570356</v>
       </c>
       <c r="AB130" s="9"/>
       <c r="AC130" s="9"/>
@@ -31937,10 +31929,10 @@
         <v>25.494703349066828</v>
       </c>
       <c r="Z131" s="19">
-        <v>27.135797289141863</v>
+        <v>27.103803121672271</v>
       </c>
       <c r="AA131" s="19">
-        <v>24.887992264134077</v>
+        <v>24.743245309549106</v>
       </c>
       <c r="AB131" s="9"/>
       <c r="AC131" s="9"/>
@@ -32501,7 +32493,7 @@
     </row>
     <row r="140" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="141" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -32512,7 +32504,7 @@
     </row>
     <row r="143" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="144" spans="1:96" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -32715,10 +32707,10 @@
         <v>15.562528249956841</v>
       </c>
       <c r="Z149" s="19">
-        <v>16.806054781833595</v>
+        <v>16.793454577830627</v>
       </c>
       <c r="AA149" s="19">
-        <v>19.50143891188733</v>
+        <v>19.643983051421632</v>
       </c>
       <c r="AB149" s="9"/>
       <c r="AC149" s="9"/>
@@ -32867,10 +32859,10 @@
         <v>12.931484003918806</v>
       </c>
       <c r="Z150" s="19">
-        <v>11.378450082848516</v>
+        <v>11.36551371786069</v>
       </c>
       <c r="AA150" s="19">
-        <v>9.52313383270209</v>
+        <v>9.5462276404464337</v>
       </c>
       <c r="AB150" s="9"/>
       <c r="AC150" s="9"/>
@@ -33019,10 +33011,10 @@
         <v>19.188808513165025</v>
       </c>
       <c r="Z151" s="19">
-        <v>18.230056098755608</v>
+        <v>18.212500630091203</v>
       </c>
       <c r="AA151" s="19">
-        <v>17.517589586367972</v>
+        <v>17.523474354463719</v>
       </c>
       <c r="AB151" s="9"/>
       <c r="AC151" s="9"/>
@@ -33171,10 +33163,10 @@
         <v>14.165848090491151</v>
       </c>
       <c r="Z152" s="19">
-        <v>13.641611405601624</v>
+        <v>13.730407371638279</v>
       </c>
       <c r="AA152" s="19">
-        <v>13.753997038681117</v>
+        <v>13.845111804733884</v>
       </c>
       <c r="AB152" s="9"/>
       <c r="AC152" s="9"/>
@@ -33323,10 +33315,10 @@
         <v>5.591184727582605</v>
       </c>
       <c r="Z153" s="19">
-        <v>5.5130172340687515</v>
+        <v>5.5067493854070424</v>
       </c>
       <c r="AA153" s="19">
-        <v>5.0742092732086395</v>
+        <v>5.0439075950345291</v>
       </c>
       <c r="AB153" s="9"/>
       <c r="AC153" s="9"/>
@@ -33475,10 +33467,10 @@
         <v>32.56014641488558</v>
       </c>
       <c r="Z154" s="19">
-        <v>34.4308103968919</v>
+        <v>34.391374317172172</v>
       </c>
       <c r="AA154" s="19">
-        <v>34.629631357152846</v>
+        <v>34.397295553899795</v>
       </c>
       <c r="AB154" s="9"/>
       <c r="AC154" s="9"/>
